--- a/files_result_10.07.2025/Поставщики комплектующих.xlsx
+++ b/files_result_10.07.2025/Поставщики комплектующих.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DC3772-03A8-4923-B4DC-7D85016921D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AC0EE0-99F1-4F2B-A770-C7055DD45380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="80">
   <si>
     <t>дата поставки</t>
   </si>
@@ -264,6 +264,24 @@
   </si>
   <si>
     <t>02.06.2025</t>
+  </si>
+  <si>
+    <t>20.05.2025</t>
+  </si>
+  <si>
+    <t>Пленка Сметана зелень</t>
+  </si>
+  <si>
+    <t>Пленка Васаби</t>
+  </si>
+  <si>
+    <t>Пленка Сыр с луком</t>
+  </si>
+  <si>
+    <t>Пленка Барбекю</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гофрокороб 460*340*130 </t>
   </si>
 </sst>
 </file>
@@ -3212,104 +3230,128 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
+      <c r="A24" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="B24" s="3" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C24" s="8">
-        <v>42.15</v>
+        <v>605</v>
       </c>
       <c r="D24" s="6">
-        <v>682</v>
+        <v>220.6</v>
       </c>
       <c r="E24" s="6">
-        <f t="shared" si="2"/>
-        <v>28746.3</v>
+        <f>C24*D24</f>
+        <v>133463</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="6"/>
       <c r="H24" s="3"/>
       <c r="I24" s="6">
         <f t="shared" si="0"/>
-        <v>-237711.34999999998</v>
+        <v>-342428.05</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="B25" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C25" s="8">
-        <v>15.42</v>
+        <v>605</v>
       </c>
       <c r="D25" s="6">
-        <v>682</v>
+        <v>185.04</v>
       </c>
       <c r="E25" s="6">
-        <f t="shared" si="2"/>
-        <v>10516.44</v>
+        <f>C25*D25</f>
+        <v>111949.2</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="6"/>
       <c r="H25" s="3"/>
       <c r="I25" s="6">
         <f t="shared" si="0"/>
-        <v>-248227.78999999998</v>
+        <v>-454377.25</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="C26" s="8">
-        <v>39.979999999999997</v>
+        <v>605</v>
       </c>
       <c r="D26" s="6">
-        <v>741</v>
+        <v>213.6</v>
       </c>
       <c r="E26" s="6">
-        <f t="shared" si="2"/>
-        <v>29625.179999999997</v>
+        <f>C26*D26</f>
+        <v>129228</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="6"/>
       <c r="H26" s="3"/>
       <c r="I26" s="6">
         <f t="shared" si="0"/>
-        <v>-277852.96999999997</v>
+        <v>-583605.25</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="6"/>
+      <c r="A27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="8">
+        <v>605</v>
+      </c>
+      <c r="D27" s="6">
+        <v>193.3</v>
+      </c>
       <c r="E27" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>C27*D27</f>
+        <v>116946.5</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="6"/>
       <c r="H27" s="3"/>
       <c r="I27" s="6">
         <f t="shared" si="0"/>
-        <v>-277852.96999999997</v>
+        <v>-700551.75</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="6"/>
+      <c r="A28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="8">
+        <v>414</v>
+      </c>
+      <c r="D28" s="6">
+        <v>25.450000000000031</v>
+      </c>
       <c r="E28" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>C28*D28</f>
+        <v>10536.300000000014</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="6"/>
       <c r="H28" s="3"/>
       <c r="I28" s="6">
         <f t="shared" si="0"/>
-        <v>-277852.96999999997</v>
+        <v>-711088.05</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -3319,7 +3361,7 @@
       <c r="D29" s="6"/>
       <c r="E29" s="6">
         <f>SUM(E3:E27)</f>
-        <v>1849616.7699999998</v>
+        <v>2272315.5499999998</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="6">
@@ -5447,21 +5489,32 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
+      <c r="A24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="20">
+        <v>33</v>
+      </c>
+      <c r="D24" s="21">
+        <v>290</v>
+      </c>
+      <c r="E24" s="21">
+        <f>C24*D24</f>
+        <v>9570</v>
+      </c>
       <c r="F24" s="3" t="s">
         <v>73</v>
       </c>
       <c r="G24" s="6">
-        <v>245268</v>
+        <v>45</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="21">
         <f t="shared" si="0"/>
-        <v>209196.796</v>
+        <v>-45596.203999999998</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -5475,7 +5528,7 @@
       <c r="H25" s="3"/>
       <c r="I25" s="21">
         <f t="shared" si="0"/>
-        <v>209196.796</v>
+        <v>-45596.203999999998</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -5489,7 +5542,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="21">
         <f t="shared" si="0"/>
-        <v>209196.796</v>
+        <v>-45596.203999999998</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -5503,7 +5556,7 @@
       <c r="H27" s="3"/>
       <c r="I27" s="21">
         <f t="shared" si="0"/>
-        <v>209196.796</v>
+        <v>-45596.203999999998</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -5517,7 +5570,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="21">
         <f t="shared" si="0"/>
-        <v>209196.796</v>
+        <v>-45596.203999999998</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -5531,21 +5584,21 @@
       <c r="H29" s="3"/>
       <c r="I29" s="21">
         <f t="shared" si="0"/>
-        <v>209196.796</v>
+        <v>-45596.203999999998</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E30" s="37">
         <f>SUM(E3:E27)</f>
-        <v>1055498.804</v>
+        <v>1065068.804</v>
       </c>
       <c r="G30" s="7">
         <f>SUM(G2:G28)</f>
-        <v>1264695.6000000001</v>
+        <v>1019472.6</v>
       </c>
       <c r="I30" s="37">
         <f>G30-E30</f>
-        <v>209196.79600000009</v>
+        <v>-45596.204000000027</v>
       </c>
     </row>
   </sheetData>
